--- a/output/validation_results.xlsx
+++ b/output/validation_results.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validation Results'!$A$1:$R$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$B$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Validation Results'!$A$1:$R$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Summary'!$A$1:$B$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -40,7 +40,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +50,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -70,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -79,6 +84,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -462,21 +470,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:R28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -600,17 +608,17 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>INVALID_DOMAIN</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Domain 'koraorganics.com' does not exist</t>
+          <t>Server disconnected (koraorganics-com.mail.protection.outlook.com): Server not connected</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Domain 'koraorganics.com' does not exist</t>
+          <t>Server disconnected (koraorganics-com.mail.protection.outlook.com): Server not connected</t>
         </is>
       </c>
       <c r="H2" s="2" t="b">
@@ -622,21 +630,35 @@
       <c r="J2" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (koraorganics-com.mail.protection.outlook.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>2054.8</v>
+        <v>4694.15</v>
       </c>
     </row>
     <row r="3">
@@ -662,17 +684,17 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>INVALID_DOMAIN</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Domain 'oneloveorganics.com' does not exist</t>
+          <t>Server disconnected (mx2-us1.ppe-hosted.com): Server not connected</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Domain 'oneloveorganics.com' does not exist</t>
+          <t>Server disconnected (mx2-us1.ppe-hosted.com): Server not connected</t>
         </is>
       </c>
       <c r="H3" s="2" t="b">
@@ -684,21 +706,35 @@
       <c r="J3" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
-      <c r="N3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx2-us1.ppe-hosted.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>2080.03</v>
+        <v>17191.81</v>
       </c>
     </row>
     <row r="4">
@@ -724,17 +760,17 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>INVALID_DOMAIN</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Domain 'wareiq.com' does not exist</t>
+          <t>Network error (alt4.aspmx.l.googlemail.com): [Errno 11001] getaddrinfo failed</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Domain 'wareiq.com' does not exist</t>
+          <t>Network error (alt4.aspmx.l.googlemail.com): [Errno 11001] getaddrinfo failed</t>
         </is>
       </c>
       <c r="H4" s="2" t="b">
@@ -746,21 +782,35 @@
       <c r="J4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr"/>
-      <c r="N4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Network error (alt4.aspmx.l.googlemail.com): [Errno 11001] getaddrinfo failed</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="P4" s="2" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>2103.28</v>
+        <v>6580.02</v>
       </c>
     </row>
     <row r="5">
@@ -786,17 +836,17 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>INVALID_DOMAIN</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Domain 'theorganicriot.com' does not exist</t>
+          <t>Server disconnected (aspmx2.googlemail.com): Server not connected</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Domain 'theorganicriot.com' does not exist</t>
+          <t>Server disconnected (aspmx2.googlemail.com): Server not connected</t>
         </is>
       </c>
       <c r="H5" s="2" t="b">
@@ -808,21 +858,35 @@
       <c r="J5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx2.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="P5" s="2" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>2111.3</v>
+        <v>26226.06</v>
       </c>
     </row>
     <row r="6">
@@ -848,17 +912,17 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>INVALID_DOMAIN</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Domain 'forest-riot.com' does not exist</t>
+          <t>Server disconnected (smtp.google.com): Server not connected</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Domain 'forest-riot.com' does not exist</t>
+          <t>Server disconnected (smtp.google.com): Server not connected</t>
         </is>
       </c>
       <c r="H6" s="2" t="b">
@@ -870,21 +934,35 @@
       <c r="J6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (smtp.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="P6" s="2" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>2066.74</v>
+        <v>12933.56</v>
       </c>
     </row>
     <row r="7">
@@ -910,17 +988,17 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>INVALID_DOMAIN</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Domain 'nakedallnatural.com' does not exist</t>
+          <t>Server disconnected (mail.nakedallnatural.com): Connection unexpectedly closed: timed out</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Domain 'nakedallnatural.com' does not exist</t>
+          <t>Server disconnected (mail.nakedallnatural.com): Connection unexpectedly closed: timed out</t>
         </is>
       </c>
       <c r="H7" s="2" t="b">
@@ -932,21 +1010,35 @@
       <c r="J7" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mail.nakedallnatural.com): Connection unexpectedly closed: timed out</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="P7" s="2" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>2121.88</v>
+        <v>19128.11</v>
       </c>
     </row>
     <row r="8">
@@ -972,17 +1064,17 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>INVALID_DOMAIN</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Domain 'nakednature.in' does not exist</t>
+          <t>Server disconnected (mx.nakednature.in.cust.b.hostedemail.com): Connection unexpectedly closed: [WinError 10054] An existing connection was forcibly closed by the remote host</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Domain 'nakednature.in' does not exist</t>
+          <t>Server disconnected (mx.nakednature.in.cust.b.hostedemail.com): Connection unexpectedly closed: [WinError 10054] An existing connection was forcibly closed by the remote host</t>
         </is>
       </c>
       <c r="H8" s="2" t="b">
@@ -994,21 +1086,35 @@
       <c r="J8" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.nakednature.in.cust.b.hostedemail.com): Connection unexpectedly closed: [WinError 10054] An existing connection was forcibly closed by the remote host</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="P8" s="2" t="n">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>2046.82</v>
+        <v>3387.16</v>
       </c>
     </row>
     <row r="9">
@@ -1034,53 +1140,1495 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.nakednature.in.cust.b.hostedemail.com): Connection unexpectedly closed: [WinError 10054] An existing connection was forcibly closed by the remote host</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.nakednature.in.cust.b.hostedemail.com): Connection unexpectedly closed: [WinError 10054] An existing connection was forcibly closed by the remote host</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.nakednature.in.cust.b.hostedemail.com): Connection unexpectedly closed: [WinError 10054] An existing connection was forcibly closed by the remote host</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q9" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R9" s="2" t="n">
+        <v>3298.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>cuma.meroan@gq.comal</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>cuma.meroan@gq.comal</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>gq.comal</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
           <t>INVALID_DOMAIN</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Domain 'nakednature.in' does not exist</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Domain 'nakednature.in' does not exist</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="n">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Domain 'gq.comal' does not exist</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Domain 'gq.comal' does not exist</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O10" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="P9" s="2" t="n">
+      <c r="P10" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="Q9" s="2" t="n">
+      <c r="Q10" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="R9" s="2" t="n">
-        <v>2056.51</v>
+      <c r="R10" s="2" t="n">
+        <v>178.56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>support@oracura.in</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>support@oracura.in</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>oracura.in</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx3.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx3.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx3.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>8760.799999999999</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>hr@oracura.in</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>hr@oracura.in</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>oracura.in</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx3.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx3.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx3.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>14843.45</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>info@cannarma.com</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>info@cannarma.com</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>cannarma.com</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt3.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt3.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt3.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>7942.31</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>support@cannarma.com</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>support@cannarma.com</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>cannarma.com</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt3.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt3.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt3.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>8631.98</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>example@gmail.com</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>example@gmail.com</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>gmail.com</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt4.gmail-smtp-in.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt4.gmail-smtp-in.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt4.gmail-smtp-in.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>8113.31</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>info@thebrownbear.ca</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>info@thebrownbear.ca</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>thebrownbear.ca</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx3.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx3.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx3.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>5988.06</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>care@mycarmesi.com</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>care@mycarmesi.com</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>mycarmesi.com</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx2.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx2.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (aspmx2.googlemail.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>15626.67</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>support@daybreak-official.com</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>support@daybreak-official.com</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>daybreak-official.com</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Timeout connecting to daybreak-official.com</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Timeout connecting to daybreak-official.com</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Timeout connecting to daybreak-official.com</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>30204.35</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>mohammadweex21@gmail.com</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>mohammadweex21@gmail.com</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>gmail.com</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt4.gmail-smtp-in.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt4.gmail-smtp-in.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt4.gmail-smtp-in.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>8148.87</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>community@thedearist.com</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>community@thedearist.com</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>thedearist.com</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt3.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt3.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt3.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>8212.799999999999</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>admin@thedearist.com</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>admin@thedearist.com</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>thedearist.com</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt3.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt3.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt3.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>14848.09</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>customersupport@betterdaysco.com</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>customersupport@betterdaysco.com</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>betterdaysco.com</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt4.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt4.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt4.aspmx.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>6464.61</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>info@daysahead.nl</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>info@daysahead.nl</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>daysahead.nl</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>INVALID_DOMAIN</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Domain 'daysahead.nl' does not exist</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>Domain 'daysahead.nl' does not exist</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="n">
+        <v/>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>196.75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>messages@territoryahead.com</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>messages@territoryahead.com</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>territoryahead.com</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (territoryahead-com.mail.protection.outlook.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (territoryahead-com.mail.protection.outlook.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (territoryahead-com.mail.protection.outlook.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>3227.84</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>support@dentalkart.com</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>support@dentalkart.com</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>dentalkart.com</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.zoho.in): Server not connected</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.zoho.in): Server not connected</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.zoho.in): Server not connected</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>3831.7</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>returns@dentalkart.com</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>returns@dentalkart.com</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>dentalkart.com</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.zoho.in): Server not connected</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.zoho.in): Server not connected</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.zoho.in): Server not connected</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>9780.620000000001</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>cs@dentalkart.com</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>cs@dentalkart.com</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>dentalkart.com</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>CORPORATE_OR_CUSTOM</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.zoho.in): Server not connected</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.zoho.in): Server not connected</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (mx.zoho.in): Server not connected</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>3860</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>manasdikshit48@gmail.com</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>manasdikshit48@gmail.com</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>gmail.com</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt4.gmail-smtp-in.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt4.gmail-smtp-in.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Server disconnected (alt4.gmail-smtp-in.l.google.com): Server not connected</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>8156.99</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R9"/>
-  <conditionalFormatting sqref="O2:O9">
+  <autoFilter ref="A1:R28"/>
+  <conditionalFormatting sqref="O2:O28">
     <cfRule type="cellIs" priority="1" operator="greaterThanOrEqual" dxfId="0" stopIfTrue="1">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q9">
+  <conditionalFormatting sqref="Q2:Q28">
     <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="1" stopIfTrue="1">
       <formula>50</formula>
     </cfRule>
@@ -1095,7 +2643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -1121,7 +2669,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -1141,7 +2689,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -1171,7 +2719,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8"/>
@@ -1190,75 +2738,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nakednature.in</t>
+          <t>gmail.com</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>koraorganics.com</t>
+          <t>dentalkart.com</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>oneloveorganics.com</t>
+          <t>nakednature.in</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>wareiq.com</t>
+          <t>oracura.in</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>theorganicriot.com</t>
+          <t>cannarma.com</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>forest-riot.com</t>
+          <t>thedearist.com</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>nakedallnatural.com</t>
+          <t>koraorganics.com</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>1</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>oneloveorganics.com</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>wareiq.com</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>theorganicriot.com</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B16"/>
+  <autoFilter ref="A1:B19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>